--- a/livres_ext.xlsx
+++ b/livres_ext.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="39">
   <si>
     <t>Première phrase</t>
   </si>
@@ -73,6 +73,63 @@
   </si>
   <si>
     <t>Cyrano de Bergerac - Edmond Rostand</t>
+  </si>
+  <si>
+    <t>Les Deux-Pattes - ni toi - n’entendent rien à l’égoïsme, à celui des Chats… Ils baptisent ainsi, pêle-mêle, l’instinct de préservation, la pudique réserve, la dignité, le renoncement fatigué qui nous vient de l’impossibilité d’être compris par eux. Chien peu distingué, mais dénué de parti pris, me comprendras-tu mieux ? Le Chat est un hôte et non un jouet. En vérité, je ne sais en quel temps nous vivons ! Les Deux-Pattes, Lui et Elle, ont-ils seuls le droit de s’attrister, de se réjouir, de lapper les assiettes, de gronder, de promener par la maison une humeur capricieuse ? J’ai, moi aussi, MES caprices, MA tristesse, mon appétit inégal, mes heures de retraite rêveuse où je me sépare du monde….</t>
+  </si>
+  <si>
+    <t>Dialogues de Bêtes - Colette</t>
+  </si>
+  <si>
+    <t>La fillette du premier plan, la plus belle de toutes, était Eléa, reconnaissable et différente. Différente moins à cause de l’âge que de la paix et de la joie qui illuminaient son visage. Le garçon qui était debout près d’elle la regardait, et elle regardait le garçon. Il était blond comme le blé mûr au soleil. Ses cheveux lisses tombaient droit autour de son visage jusqu’à ses épaules fines où déjà les muscles esquissaient leur galbe enveloppé. Ses yeux noisettes regardaient dans le miroir les yeux bleus d’Elsa, et leur souriaient.</t>
+  </si>
+  <si>
+    <t>La nuit des temps - Barjavel</t>
+  </si>
+  <si>
+    <t>Petite âme, âme tendre et flottante, comparé de mon corps, qui fut ton hôte, tu vas descendre dans ces lieux pâles, durs et nus, où tu devras renoncer aux jeux d’autrefois. Un instant encore, regardons ensemble les rives familières, les objets que sans doute nous ne reverrons plus… Tâchons d’entrer dans la mort les yeux ouverts…</t>
+  </si>
+  <si>
+    <t>Mémoires d’Hadrien - Marguerite Yourcenar</t>
+  </si>
+  <si>
+    <t>Quand la porte de sa cellule se fut refermée sur lui à grand bruit de ferraille, Zénon pensif tira l’escabeau et s’assit devant la table. Il faisait encore grand jour, l’obscure prison des allégories alchimiques étant dans son cas une prison fort claire. A travers le réseau serré du grillage qui protégeait la croisée, une blancheur plombée montait de la cour couverte de neige.</t>
+  </si>
+  <si>
+    <t>L’Oeuvre au Noir - Marguerite Yourcenar</t>
+  </si>
+  <si>
+    <t>Quand je suis sorti, il était midi, je suis resté sur le trottoir et quand on me demandait comment allait Madame Rosa, je disais qu’elle était partie dans son foyer juif en Israël, sa famille était venue la chercher, elle avait là-bas le confort moderne et allait mourir beaucoup plus vite qu’ici où c’était pas une vie pour elle.</t>
+  </si>
+  <si>
+    <t>La vie devant soi - Romain Gary</t>
+  </si>
+  <si>
+    <t>Vous que dans votre enfer mon âme a poursuivies, Pauvres soeurs, je vous aime autant que je vous plains, Pour vos mornes douleurs, vos soifs inassouvies, et les urnes d’amour dont vos grands coeurs sont pleins !</t>
+  </si>
+  <si>
+    <t>Les fleurs du mal - Baudelaire</t>
+  </si>
+  <si>
+    <t>Le blé pour moi est inutile. Les champs de blé ne me rappellent rien. Et ça, c’est triste ! Mais tu as les cheveux couleur d’or. Alors ce sera merveilleux quand tu m’auras apprivoisé ! Le blé, qui est doré, me fera souvenir de toi. Et j’aimerai le bruit du vent dans le blé…</t>
+  </si>
+  <si>
+    <t>Le Petit Prince - Saint Exupéry</t>
+  </si>
+  <si>
+    <t>Il s’étalait en plein jour, tournait la nuque, ouvrait tout grands ses yeux qui semblaient noirs, mais dont Léa connaissait la sombre couleur brune et rousse. Elle toucha de l’index, comme pour désigner et choisir ce qu’il y avait de plus rare dans tant de beauté, les sourcils, les paupières, les coins de la bouche. Par moments, la forme de cet amant qu’elle méprisait un peu lui inspirait une sorte de respect. « être beau à ce point-là, c’est une noblesse », pensait-elle.</t>
+  </si>
+  <si>
+    <t>Chéri - Colette</t>
+  </si>
+  <si>
+    <t>Il s’inclina et partit, de la même façon modeste et mystérieuse qu’il avait surgi parmi nous. J’étais le seul à savoir pourquoi cet homme ne toucherait jamais plus à un échiquier, alors que les autres se sentirent un peu désarçonnés, avec la vague impression d’avoir échappé d’extrême justesse à quelque chose de désagréable ou même à un danger.</t>
+  </si>
+  <si>
+    <t>Le Joueur d’échecs - Stefan Zweig</t>
+  </si>
+  <si>
+    <t>J’ignorais la douceur féminine. Ma mère ne m’a pas trouvé beau. Je n’ai pas eu de soeur. Plus tard, j’ai redouté l’amante à l’oeil moqueur. Je vous dois d’avoir eu, tout au moins, une amie. Grâce à vous une robe a passé dans ma vie.</t>
   </si>
 </sst>
 </file>
@@ -1353,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="70" style="1" customWidth="1"/>
@@ -1395,7 +1452,7 @@
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" ht="40" customHeight="1">
+    <row r="4" ht="61.85" customHeight="1">
       <c r="A4" t="s" s="7">
         <v>6</v>
       </c>
@@ -1406,7 +1463,7 @@
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" ht="40" customHeight="1">
+    <row r="5" ht="68.9" customHeight="1">
       <c r="A5" t="s" s="9">
         <v>8</v>
       </c>
@@ -1417,7 +1474,7 @@
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" ht="40" customHeight="1">
+    <row r="6" ht="96.1" customHeight="1">
       <c r="A6" t="s" s="7">
         <v>10</v>
       </c>
@@ -1428,7 +1485,7 @@
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" ht="40" customHeight="1">
+    <row r="7" ht="71.35" customHeight="1">
       <c r="A7" t="s" s="9">
         <v>12</v>
       </c>
@@ -1450,7 +1507,7 @@
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" ht="40" customHeight="1">
+    <row r="9" ht="68.5" customHeight="1">
       <c r="A9" t="s" s="9">
         <v>16</v>
       </c>
@@ -1471,6 +1528,116 @@
       <c r="C10" s="8"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
+    </row>
+    <row r="11" ht="136" customHeight="1">
+      <c r="A11" t="s" s="7">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s" s="7">
+        <v>21</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" ht="136" customHeight="1">
+      <c r="A12" t="s" s="7">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s" s="7">
+        <v>23</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" ht="136" customHeight="1">
+      <c r="A13" t="s" s="7">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s" s="7">
+        <v>25</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" ht="136" customHeight="1">
+      <c r="A14" t="s" s="7">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s" s="7">
+        <v>27</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" ht="136" customHeight="1">
+      <c r="A15" t="s" s="7">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s" s="7">
+        <v>29</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" ht="136" customHeight="1">
+      <c r="A16" t="s" s="7">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s" s="7">
+        <v>31</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" ht="136" customHeight="1">
+      <c r="A17" t="s" s="7">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s" s="7">
+        <v>33</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" ht="136" customHeight="1">
+      <c r="A18" t="s" s="7">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s" s="7">
+        <v>35</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19" ht="136" customHeight="1">
+      <c r="A19" t="s" s="7">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s" s="7">
+        <v>37</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+    </row>
+    <row r="20" ht="136" customHeight="1">
+      <c r="A20" t="s" s="7">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
